--- a/data/Zanderij_monthly.xlsx
+++ b/data/Zanderij_monthly.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\OneDrive\Documents\Data_Website\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\My PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AC52C6-160F-47E5-9409-D8C759C3EFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6321A59B-F58D-4714-952C-458B645530D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4645E167-86B9-4E45-866C-5B881B13017F}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4645E167-86B9-4E45-866C-5B881B13017F}"/>
   </bookViews>
   <sheets>
     <sheet name="data_products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -889,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B716C3A-09DE-493B-8CA8-22DE291B800F}">
-  <dimension ref="A1:C787"/>
+  <dimension ref="A1:C800"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -9326,32 +9339,32 @@
         <v>2023</v>
       </c>
       <c r="B767">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C767">
-        <v>60.7</v>
+        <v>37.299999999999997</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A768">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B768">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C768">
-        <v>104.7</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A769">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B769">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C769">
-        <v>41.2</v>
+        <v>93.6</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.25">
@@ -9359,10 +9372,10 @@
         <v>2024</v>
       </c>
       <c r="B770">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C770">
-        <v>84.7</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.25">
@@ -9370,10 +9383,10 @@
         <v>2024</v>
       </c>
       <c r="B771">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C771">
-        <v>255.2</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.25">
@@ -9381,10 +9394,10 @@
         <v>2024</v>
       </c>
       <c r="B772">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C772">
-        <v>482.1</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.25">
@@ -9392,10 +9405,10 @@
         <v>2024</v>
       </c>
       <c r="B773">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C773">
-        <v>387.1</v>
+        <v>255.2</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.25">
@@ -9403,10 +9416,10 @@
         <v>2024</v>
       </c>
       <c r="B774">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C774">
-        <v>137.9</v>
+        <v>482.1</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.25">
@@ -9414,10 +9427,10 @@
         <v>2024</v>
       </c>
       <c r="B775">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C775">
-        <v>102.5</v>
+        <v>387.1</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.25">
@@ -9425,10 +9438,10 @@
         <v>2024</v>
       </c>
       <c r="B776">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C776">
-        <v>55.5</v>
+        <v>137.9</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.25">
@@ -9436,10 +9449,10 @@
         <v>2024</v>
       </c>
       <c r="B777">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C777">
-        <v>118.2</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
@@ -9447,10 +9460,10 @@
         <v>2024</v>
       </c>
       <c r="B778">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C778">
-        <v>88.2</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
@@ -9458,32 +9471,32 @@
         <v>2024</v>
       </c>
       <c r="B779">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C779">
-        <v>232.3</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A780">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B780">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C780">
-        <v>162</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A781">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B781">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C781">
-        <v>179</v>
+        <v>232.3</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.25">
@@ -9491,10 +9504,10 @@
         <v>2025</v>
       </c>
       <c r="B782">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C782">
-        <v>90.1</v>
+        <v>162</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.25">
@@ -9502,10 +9515,10 @@
         <v>2025</v>
       </c>
       <c r="B783">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C783">
-        <v>378.9</v>
+        <v>179</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.25">
@@ -9513,10 +9526,10 @@
         <v>2025</v>
       </c>
       <c r="B784">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C784">
-        <v>426</v>
+        <v>90.1</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.25">
@@ -9524,10 +9537,10 @@
         <v>2025</v>
       </c>
       <c r="B785">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C785">
-        <v>82.6</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.25">
@@ -9535,10 +9548,10 @@
         <v>2025</v>
       </c>
       <c r="B786">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C786">
-        <v>96.3</v>
+        <v>378.9</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.25">
@@ -9546,10 +9559,153 @@
         <v>2025</v>
       </c>
       <c r="B787">
+        <v>6</v>
+      </c>
+      <c r="C787">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A788">
+        <v>2025</v>
+      </c>
+      <c r="B788">
+        <v>7</v>
+      </c>
+      <c r="C788">
+        <v>194.8</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A789">
+        <v>2025</v>
+      </c>
+      <c r="B789">
+        <v>8</v>
+      </c>
+      <c r="C789">
+        <v>139.19999999999999</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A790">
+        <v>2025</v>
+      </c>
+      <c r="B790">
+        <v>9</v>
+      </c>
+      <c r="C790">
+        <v>82.6</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A791">
+        <v>2025</v>
+      </c>
+      <c r="B791">
+        <v>10</v>
+      </c>
+      <c r="C791">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A792">
+        <v>2025</v>
+      </c>
+      <c r="B792">
         <v>11</v>
       </c>
-      <c r="C787">
+      <c r="C792">
         <v>115.2</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A793">
+        <v>2025</v>
+      </c>
+      <c r="B793">
+        <v>12</v>
+      </c>
+      <c r="C793">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A794">
+        <v>2026</v>
+      </c>
+      <c r="B794">
+        <v>1</v>
+      </c>
+      <c r="C794">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A795">
+        <v>2026</v>
+      </c>
+      <c r="B795">
+        <v>2</v>
+      </c>
+      <c r="C795">
+        <v>64.5</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A796">
+        <v>2026</v>
+      </c>
+      <c r="B796">
+        <v>3</v>
+      </c>
+      <c r="C796">
+        <v>192.8</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A797">
+        <v>2026</v>
+      </c>
+      <c r="B797">
+        <v>4</v>
+      </c>
+      <c r="C797">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A798">
+        <v>2026</v>
+      </c>
+      <c r="B798">
+        <v>5</v>
+      </c>
+      <c r="C798">
+        <v>124.9</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A799">
+        <v>2026</v>
+      </c>
+      <c r="B799">
+        <v>6</v>
+      </c>
+      <c r="C799">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A800">
+        <v>2026</v>
+      </c>
+      <c r="B800">
+        <v>7</v>
+      </c>
+      <c r="C800">
+        <v>183.2</v>
       </c>
     </row>
   </sheetData>
